--- a/tools/importer/reports/import-lux-travel.report.xlsx
+++ b/tools/importer/reports/import-lux-travel.report.xlsx
@@ -49,7 +49,7 @@
     <t>success</t>
   </si>
   <si>
-    <t>2026-10-29T16:51:04.230Z</t>
+    <t>2026-10-29T19:40:08.115Z</t>
   </si>
   <si>
     <t>Lux Traveler | Where Every Journey Is Extraordinary</t>
